--- a/AAII_Financials/Yearly/MCHT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MCHT_YR_FIN.xlsx
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E18" s="3">
         <v>2500</v>
@@ -1053,7 +1053,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
         <v>500</v>
@@ -1449,7 +1449,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
         <v>-500</v>
